--- a/stories/arbres/TREE-SOC-048.xlsx
+++ b/stories/arbres/TREE-SOC-048.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est avec maman, au marché. Jules a envie de jouer. maman est là, tout près. On va apprendre : Un pays, un paysage. Voici le geste : nommer. Jules écoute maman. Jules entend les mots : nom, paysage.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un pays, un paysage.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : nommer. Jules respire. Jules retient : nom, paysage. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un pays, un paysage.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : nommer. Jules respire. Jules retient : nom, paysage. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : nom, paysage. Voici le geste : nommer. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un pays, un paysage.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : nommer. Jules respire. Jules retient : nom, paysage. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-048.xlsx
+++ b/stories/arbres/TREE-SOC-048.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est avec maman, au marché. Jules a envie de jouer. maman est là, tout près. On va apprendre : Un pays, un paysage. Voici le geste : nommer. Jules écoute maman. Jules entend les mots : nom, paysage.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Un pays, un paysage.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : nommer. Jules respire. Jules retient : nom, paysage. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Jules a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Jules rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Jules rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Jules rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Jules a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Jules rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Jules rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Jules rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Jules a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Jules rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Jules rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Jules rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Un pays, un paysage.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : nommer. Jules respire. Jules retient : nom, paysage. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Jules a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Jules rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Jules rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Jules rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Jules a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Jules rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Jules rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Jules rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Jules a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Jules rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Jules rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Jules rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Un pays, un paysage.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : nommer. Jules respire. Jules retient : nom, paysage. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Jules a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Jules rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Jules rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Jules rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Jules a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Jules rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Jules rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Jules rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Jules a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer. Jules répète tout bas : nom, paysage. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Jules rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Jules rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Jules rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Un pays, un paysage. Voici le geste : nommer. Jules a entendu : nom, paysage. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
